--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -35584,7 +35584,7 @@
         <v>46276.5625</v>
       </c>
       <c r="B1355" t="n">
-        <v>14265197</v>
+        <v>14344700</v>
       </c>
       <c r="C1355" t="n">
         <v>15.7799997329712</v>
@@ -35602,6 +35602,32 @@
         <v>15.2700004577637</v>
       </c>
       <c r="H1355" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" s="1" t="n">
+        <v>46279.5625</v>
+      </c>
+      <c r="B1356" t="n">
+        <v>12985213</v>
+      </c>
+      <c r="C1356" t="n">
+        <v>15.5950002670288</v>
+      </c>
+      <c r="D1356" t="n">
+        <v>14.5220003128052</v>
+      </c>
+      <c r="E1356" t="n">
+        <v>14.5319995880127</v>
+      </c>
+      <c r="F1356" t="n">
+        <v>15.2700004577637</v>
+      </c>
+      <c r="G1356" t="n">
+        <v>15.2700004577637</v>
+      </c>
+      <c r="H1356" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -35584,7 +35584,7 @@
         <v>46276.5625</v>
       </c>
       <c r="B1355" t="n">
-        <v>14344700</v>
+        <v>14392100</v>
       </c>
       <c r="C1355" t="n">
         <v>15.7799997329712</v>
@@ -35610,7 +35610,7 @@
         <v>46279.5625</v>
       </c>
       <c r="B1356" t="n">
-        <v>12985213</v>
+        <v>13018100</v>
       </c>
       <c r="C1356" t="n">
         <v>15.5950002670288</v>
@@ -35619,7 +35619,7 @@
         <v>14.5220003128052</v>
       </c>
       <c r="E1356" t="n">
-        <v>14.5319995880127</v>
+        <v>14.5500001907349</v>
       </c>
       <c r="F1356" t="n">
         <v>15.2700004577637</v>
@@ -35628,6 +35628,32 @@
         <v>15.2700004577637</v>
       </c>
       <c r="H1356" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" s="1" t="n">
+        <v>46280.5625</v>
+      </c>
+      <c r="B1357" t="n">
+        <v>12268625</v>
+      </c>
+      <c r="C1357" t="n">
+        <v>15.5299997329712</v>
+      </c>
+      <c r="D1357" t="n">
+        <v>14.9899997711182</v>
+      </c>
+      <c r="E1357" t="n">
+        <v>15.1300001144409</v>
+      </c>
+      <c r="F1357" t="n">
+        <v>15.0900001525879</v>
+      </c>
+      <c r="G1357" t="n">
+        <v>15.0900001525879</v>
+      </c>
+      <c r="H1357" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -35636,7 +35636,7 @@
         <v>46280.5625</v>
       </c>
       <c r="B1357" t="n">
-        <v>12268625</v>
+        <v>12305900</v>
       </c>
       <c r="C1357" t="n">
         <v>15.5299997329712</v>
@@ -35654,6 +35654,32 @@
         <v>15.0900001525879</v>
       </c>
       <c r="H1357" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" s="1" t="n">
+        <v>46281.5625</v>
+      </c>
+      <c r="B1358" t="n">
+        <v>13605685</v>
+      </c>
+      <c r="C1358" t="n">
+        <v>15.3199996948242</v>
+      </c>
+      <c r="D1358" t="n">
+        <v>14.4099998474121</v>
+      </c>
+      <c r="E1358" t="n">
+        <v>15.1999998092651</v>
+      </c>
+      <c r="F1358" t="n">
+        <v>14.789999961853</v>
+      </c>
+      <c r="G1358" t="n">
+        <v>14.789999961853</v>
+      </c>
+      <c r="H1358" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -35662,7 +35662,7 @@
         <v>46281.5625</v>
       </c>
       <c r="B1358" t="n">
-        <v>13605685</v>
+        <v>13746500</v>
       </c>
       <c r="C1358" t="n">
         <v>15.3199996948242</v>
@@ -35680,6 +35680,32 @@
         <v>14.789999961853</v>
       </c>
       <c r="H1358" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" s="1" t="n">
+        <v>46282.5625</v>
+      </c>
+      <c r="B1359" t="n">
+        <v>19463858</v>
+      </c>
+      <c r="C1359" t="n">
+        <v>16.1599998474121</v>
+      </c>
+      <c r="D1359" t="n">
+        <v>15.3000001907349</v>
+      </c>
+      <c r="E1359" t="n">
+        <v>15.3299999237061</v>
+      </c>
+      <c r="F1359" t="n">
+        <v>15.9899997711182</v>
+      </c>
+      <c r="G1359" t="n">
+        <v>15.9899997711182</v>
+      </c>
+      <c r="H1359" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -35688,7 +35688,7 @@
         <v>46282.5625</v>
       </c>
       <c r="B1359" t="n">
-        <v>19463858</v>
+        <v>19529800</v>
       </c>
       <c r="C1359" t="n">
         <v>16.1599998474121</v>
@@ -35706,6 +35706,32 @@
         <v>15.9899997711182</v>
       </c>
       <c r="H1359" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" s="1" t="n">
+        <v>46283.5625</v>
+      </c>
+      <c r="B1360" t="n">
+        <v>19013815</v>
+      </c>
+      <c r="C1360" t="n">
+        <v>16.3199996948242</v>
+      </c>
+      <c r="D1360" t="n">
+        <v>15.0900001525879</v>
+      </c>
+      <c r="E1360" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="F1360" t="n">
+        <v>15.7600002288818</v>
+      </c>
+      <c r="G1360" t="n">
+        <v>15.7600002288818</v>
+      </c>
+      <c r="H1360" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -35714,7 +35714,7 @@
         <v>46283.5625</v>
       </c>
       <c r="B1360" t="n">
-        <v>19013815</v>
+        <v>19157100</v>
       </c>
       <c r="C1360" t="n">
         <v>16.3199996948242</v>
@@ -35732,6 +35732,32 @@
         <v>15.7600002288818</v>
       </c>
       <c r="H1360" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" s="1" t="n">
+        <v>46286.5625</v>
+      </c>
+      <c r="B1361" t="n">
+        <v>15901838</v>
+      </c>
+      <c r="C1361" t="n">
+        <v>16.5599994659424</v>
+      </c>
+      <c r="D1361" t="n">
+        <v>16.1100006103516</v>
+      </c>
+      <c r="E1361" t="n">
+        <v>16.2999992370605</v>
+      </c>
+      <c r="F1361" t="n">
+        <v>16.5300006866455</v>
+      </c>
+      <c r="G1361" t="n">
+        <v>16.5300006866455</v>
+      </c>
+      <c r="H1361" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -35714,7 +35714,7 @@
         <v>46283.5625</v>
       </c>
       <c r="B1360" t="n">
-        <v>19157100</v>
+        <v>19229000</v>
       </c>
       <c r="C1360" t="n">
         <v>16.3199996948242</v>
@@ -35740,7 +35740,7 @@
         <v>46286.5625</v>
       </c>
       <c r="B1361" t="n">
-        <v>15901838</v>
+        <v>16732000</v>
       </c>
       <c r="C1361" t="n">
         <v>16.5599994659424</v>
@@ -35749,7 +35749,7 @@
         <v>16.1100006103516</v>
       </c>
       <c r="E1361" t="n">
-        <v>16.2999992370605</v>
+        <v>16.2099990844727</v>
       </c>
       <c r="F1361" t="n">
         <v>16.5300006866455</v>
@@ -35758,6 +35758,32 @@
         <v>16.5300006866455</v>
       </c>
       <c r="H1361" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" s="1" t="n">
+        <v>46287.5625</v>
+      </c>
+      <c r="B1362" t="n">
+        <v>13060977</v>
+      </c>
+      <c r="C1362" t="n">
+        <v>16.5699996948242</v>
+      </c>
+      <c r="D1362" t="n">
+        <v>16.0599994659424</v>
+      </c>
+      <c r="E1362" t="n">
+        <v>16.4850006103516</v>
+      </c>
+      <c r="F1362" t="n">
+        <v>16.5200004577637</v>
+      </c>
+      <c r="G1362" t="n">
+        <v>16.5200004577637</v>
+      </c>
+      <c r="H1362" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -35766,7 +35766,7 @@
         <v>46287.5625</v>
       </c>
       <c r="B1362" t="n">
-        <v>13060977</v>
+        <v>13847000</v>
       </c>
       <c r="C1362" t="n">
         <v>16.5699996948242</v>
@@ -35784,6 +35784,32 @@
         <v>16.5200004577637</v>
       </c>
       <c r="H1362" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" s="1" t="n">
+        <v>46288.5625</v>
+      </c>
+      <c r="B1363" t="n">
+        <v>27144180</v>
+      </c>
+      <c r="C1363" t="n">
+        <v>17.6599998474121</v>
+      </c>
+      <c r="D1363" t="n">
+        <v>15.9700002670288</v>
+      </c>
+      <c r="E1363" t="n">
+        <v>17.6280002593994</v>
+      </c>
+      <c r="F1363" t="n">
+        <v>16.0049991607666</v>
+      </c>
+      <c r="G1363" t="n">
+        <v>16.0049991607666</v>
+      </c>
+      <c r="H1363" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -35792,7 +35792,7 @@
         <v>46288.5625</v>
       </c>
       <c r="B1363" t="n">
-        <v>27144180</v>
+        <v>27251500</v>
       </c>
       <c r="C1363" t="n">
         <v>17.6599998474121</v>
@@ -35801,7 +35801,7 @@
         <v>15.9700002670288</v>
       </c>
       <c r="E1363" t="n">
-        <v>17.6280002593994</v>
+        <v>17.625</v>
       </c>
       <c r="F1363" t="n">
         <v>16.0049991607666</v>
@@ -35810,6 +35810,32 @@
         <v>16.0049991607666</v>
       </c>
       <c r="H1363" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" s="1" t="n">
+        <v>46289.5625</v>
+      </c>
+      <c r="B1364" t="n">
+        <v>18930002</v>
+      </c>
+      <c r="C1364" t="n">
+        <v>16.6000003814697</v>
+      </c>
+      <c r="D1364" t="n">
+        <v>15.6000995635986</v>
+      </c>
+      <c r="E1364" t="n">
+        <v>15.6700000762939</v>
+      </c>
+      <c r="F1364" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G1364" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H1364" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -35818,13 +35818,13 @@
         <v>46289.5625</v>
       </c>
       <c r="B1364" t="n">
-        <v>18930002</v>
+        <v>18966600</v>
       </c>
       <c r="C1364" t="n">
         <v>16.6000003814697</v>
       </c>
       <c r="D1364" t="n">
-        <v>15.6000995635986</v>
+        <v>15.6000003814697</v>
       </c>
       <c r="E1364" t="n">
         <v>15.6700000762939</v>
@@ -35836,6 +35836,32 @@
         <v>16.5</v>
       </c>
       <c r="H1364" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" s="1" t="n">
+        <v>46290.5625</v>
+      </c>
+      <c r="B1365" t="n">
+        <v>17459020</v>
+      </c>
+      <c r="C1365" t="n">
+        <v>17.2950992584229</v>
+      </c>
+      <c r="D1365" t="n">
+        <v>16.3600006103516</v>
+      </c>
+      <c r="E1365" t="n">
+        <v>16.4799995422363</v>
+      </c>
+      <c r="F1365" t="n">
+        <v>16.6599998474121</v>
+      </c>
+      <c r="G1365" t="n">
+        <v>16.6599998474121</v>
+      </c>
+      <c r="H1365" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -35844,16 +35844,16 @@
         <v>46290.5625</v>
       </c>
       <c r="B1365" t="n">
-        <v>17459020</v>
+        <v>17515200</v>
       </c>
       <c r="C1365" t="n">
-        <v>17.2950992584229</v>
+        <v>17.2950000762939</v>
       </c>
       <c r="D1365" t="n">
         <v>16.3600006103516</v>
       </c>
       <c r="E1365" t="n">
-        <v>16.4799995422363</v>
+        <v>16.4850006103516</v>
       </c>
       <c r="F1365" t="n">
         <v>16.6599998474121</v>
@@ -35862,6 +35862,32 @@
         <v>16.6599998474121</v>
       </c>
       <c r="H1365" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" s="1" t="n">
+        <v>46293.5625</v>
+      </c>
+      <c r="B1366" t="n">
+        <v>12908553</v>
+      </c>
+      <c r="C1366" t="n">
+        <v>16.7000007629395</v>
+      </c>
+      <c r="D1366" t="n">
+        <v>15.8900003433228</v>
+      </c>
+      <c r="E1366" t="n">
+        <v>16.4500007629395</v>
+      </c>
+      <c r="F1366" t="n">
+        <v>15.9499998092651</v>
+      </c>
+      <c r="G1366" t="n">
+        <v>15.9499998092651</v>
+      </c>
+      <c r="H1366" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -35844,7 +35844,7 @@
         <v>46290.5625</v>
       </c>
       <c r="B1365" t="n">
-        <v>17515200</v>
+        <v>17541300</v>
       </c>
       <c r="C1365" t="n">
         <v>17.2950000762939</v>
@@ -35870,7 +35870,7 @@
         <v>46293.5625</v>
       </c>
       <c r="B1366" t="n">
-        <v>12908553</v>
+        <v>13140400</v>
       </c>
       <c r="C1366" t="n">
         <v>16.7000007629395</v>
@@ -35888,6 +35888,32 @@
         <v>15.9499998092651</v>
       </c>
       <c r="H1366" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" s="1" t="n">
+        <v>46294.5625</v>
+      </c>
+      <c r="B1367" t="n">
+        <v>13072124</v>
+      </c>
+      <c r="C1367" t="n">
+        <v>16.4200000762939</v>
+      </c>
+      <c r="D1367" t="n">
+        <v>15.7299995422363</v>
+      </c>
+      <c r="E1367" t="n">
+        <v>16.4200000762939</v>
+      </c>
+      <c r="F1367" t="n">
+        <v>15.7399997711182</v>
+      </c>
+      <c r="G1367" t="n">
+        <v>15.7399997711182</v>
+      </c>
+      <c r="H1367" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -35896,16 +35896,16 @@
         <v>46294.5625</v>
       </c>
       <c r="B1367" t="n">
-        <v>13072124</v>
+        <v>13143900</v>
       </c>
       <c r="C1367" t="n">
-        <v>16.4200000762939</v>
+        <v>16.4249992370605</v>
       </c>
       <c r="D1367" t="n">
         <v>15.7299995422363</v>
       </c>
       <c r="E1367" t="n">
-        <v>16.4200000762939</v>
+        <v>16.3799991607666</v>
       </c>
       <c r="F1367" t="n">
         <v>15.7399997711182</v>
@@ -35914,6 +35914,32 @@
         <v>15.7399997711182</v>
       </c>
       <c r="H1367" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" s="1" t="n">
+        <v>46295.5625</v>
+      </c>
+      <c r="B1368" t="n">
+        <v>13917967</v>
+      </c>
+      <c r="C1368" t="n">
+        <v>16.5275001525879</v>
+      </c>
+      <c r="D1368" t="n">
+        <v>15.6999998092651</v>
+      </c>
+      <c r="E1368" t="n">
+        <v>15.8649997711182</v>
+      </c>
+      <c r="F1368" t="n">
+        <v>15.7399997711182</v>
+      </c>
+      <c r="G1368" t="n">
+        <v>15.7399997711182</v>
+      </c>
+      <c r="H1368" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -35922,16 +35922,16 @@
         <v>46295.5625</v>
       </c>
       <c r="B1368" t="n">
-        <v>13917967</v>
+        <v>14036000</v>
       </c>
       <c r="C1368" t="n">
-        <v>16.5275001525879</v>
+        <v>16.5279998779297</v>
       </c>
       <c r="D1368" t="n">
         <v>15.6999998092651</v>
       </c>
       <c r="E1368" t="n">
-        <v>15.8649997711182</v>
+        <v>15.8549995422363</v>
       </c>
       <c r="F1368" t="n">
         <v>15.7399997711182</v>
@@ -35940,6 +35940,32 @@
         <v>15.7399997711182</v>
       </c>
       <c r="H1368" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" s="1" t="n">
+        <v>46296.5625</v>
+      </c>
+      <c r="B1369" t="n">
+        <v>12749639</v>
+      </c>
+      <c r="C1369" t="n">
+        <v>15.9799995422363</v>
+      </c>
+      <c r="D1369" t="n">
+        <v>15.5100002288818</v>
+      </c>
+      <c r="E1369" t="n">
+        <v>15.7600002288818</v>
+      </c>
+      <c r="F1369" t="n">
+        <v>15.6199998855591</v>
+      </c>
+      <c r="G1369" t="n">
+        <v>15.6199998855591</v>
+      </c>
+      <c r="H1369" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -35948,10 +35948,10 @@
         <v>46296.5625</v>
       </c>
       <c r="B1369" t="n">
-        <v>12749639</v>
+        <v>12809900</v>
       </c>
       <c r="C1369" t="n">
-        <v>15.9799995422363</v>
+        <v>15.9849996566772</v>
       </c>
       <c r="D1369" t="n">
         <v>15.5100002288818</v>
@@ -35966,6 +35966,32 @@
         <v>15.6199998855591</v>
       </c>
       <c r="H1369" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" s="1" t="n">
+        <v>46297.5625</v>
+      </c>
+      <c r="B1370" t="n">
+        <v>13675426</v>
+      </c>
+      <c r="C1370" t="n">
+        <v>16.1049995422363</v>
+      </c>
+      <c r="D1370" t="n">
+        <v>15.1499996185303</v>
+      </c>
+      <c r="E1370" t="n">
+        <v>16.0599994659424</v>
+      </c>
+      <c r="F1370" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="G1370" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="H1370" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -35974,7 +35974,7 @@
         <v>46297.5625</v>
       </c>
       <c r="B1370" t="n">
-        <v>13675426</v>
+        <v>13696000</v>
       </c>
       <c r="C1370" t="n">
         <v>16.1049995422363</v>
@@ -35983,7 +35983,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="E1370" t="n">
-        <v>16.0599994659424</v>
+        <v>16.0550003051758</v>
       </c>
       <c r="F1370" t="n">
         <v>15.25</v>
@@ -35992,6 +35992,32 @@
         <v>15.25</v>
       </c>
       <c r="H1370" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" s="1" t="n">
+        <v>46300.5625</v>
+      </c>
+      <c r="B1371" t="n">
+        <v>12339000</v>
+      </c>
+      <c r="C1371" t="n">
+        <v>15.3000001907349</v>
+      </c>
+      <c r="D1371" t="n">
+        <v>14.8149995803833</v>
+      </c>
+      <c r="E1371" t="n">
+        <v>15.289999961853</v>
+      </c>
+      <c r="F1371" t="n">
+        <v>15.1499996185303</v>
+      </c>
+      <c r="G1371" t="n">
+        <v>15.1499996185303</v>
+      </c>
+      <c r="H1371" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -35974,7 +35974,7 @@
         <v>46297.5625</v>
       </c>
       <c r="B1370" t="n">
-        <v>13696000</v>
+        <v>13753200</v>
       </c>
       <c r="C1370" t="n">
         <v>16.1049995422363</v>
@@ -36000,7 +36000,7 @@
         <v>46300.5625</v>
       </c>
       <c r="B1371" t="n">
-        <v>12339000</v>
+        <v>12378400</v>
       </c>
       <c r="C1371" t="n">
         <v>15.3000001907349</v>
@@ -36009,7 +36009,7 @@
         <v>14.8149995803833</v>
       </c>
       <c r="E1371" t="n">
-        <v>15.289999961853</v>
+        <v>15.25</v>
       </c>
       <c r="F1371" t="n">
         <v>15.1499996185303</v>
@@ -36018,6 +36018,32 @@
         <v>15.1499996185303</v>
       </c>
       <c r="H1371" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" s="1" t="n">
+        <v>46301.5625</v>
+      </c>
+      <c r="B1372" t="n">
+        <v>14749592</v>
+      </c>
+      <c r="C1372" t="n">
+        <v>15.7700004577637</v>
+      </c>
+      <c r="D1372" t="n">
+        <v>14.9949998855591</v>
+      </c>
+      <c r="E1372" t="n">
+        <v>15.2799997329712</v>
+      </c>
+      <c r="F1372" t="n">
+        <v>15.1700000762939</v>
+      </c>
+      <c r="G1372" t="n">
+        <v>15.1700000762939</v>
+      </c>
+      <c r="H1372" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -36026,7 +36026,7 @@
         <v>46301.5625</v>
       </c>
       <c r="B1372" t="n">
-        <v>14749592</v>
+        <v>14820300</v>
       </c>
       <c r="C1372" t="n">
         <v>15.7700004577637</v>
@@ -36044,6 +36044,32 @@
         <v>15.1700000762939</v>
       </c>
       <c r="H1372" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" s="1" t="n">
+        <v>46302.5625</v>
+      </c>
+      <c r="B1373" t="n">
+        <v>13674466</v>
+      </c>
+      <c r="C1373" t="n">
+        <v>14.8900003433228</v>
+      </c>
+      <c r="D1373" t="n">
+        <v>14.4499998092651</v>
+      </c>
+      <c r="E1373" t="n">
+        <v>14.7449998855591</v>
+      </c>
+      <c r="F1373" t="n">
+        <v>14.5900001525879</v>
+      </c>
+      <c r="G1373" t="n">
+        <v>14.5900001525879</v>
+      </c>
+      <c r="H1373" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -36052,7 +36052,7 @@
         <v>46302.5625</v>
       </c>
       <c r="B1373" t="n">
-        <v>13674466</v>
+        <v>13739200</v>
       </c>
       <c r="C1373" t="n">
         <v>14.8900003433228</v>
@@ -36070,6 +36070,32 @@
         <v>14.5900001525879</v>
       </c>
       <c r="H1373" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" s="1" t="n">
+        <v>46303.5625</v>
+      </c>
+      <c r="B1374" t="n">
+        <v>17136381</v>
+      </c>
+      <c r="C1374" t="n">
+        <v>14.6099996566772</v>
+      </c>
+      <c r="D1374" t="n">
+        <v>13.7403001785278</v>
+      </c>
+      <c r="E1374" t="n">
+        <v>14.4099998474121</v>
+      </c>
+      <c r="F1374" t="n">
+        <v>14.1400003433228</v>
+      </c>
+      <c r="G1374" t="n">
+        <v>14.1400003433228</v>
+      </c>
+      <c r="H1374" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -36078,13 +36078,13 @@
         <v>46303.5625</v>
       </c>
       <c r="B1374" t="n">
-        <v>17136381</v>
+        <v>17205400</v>
       </c>
       <c r="C1374" t="n">
         <v>14.6099996566772</v>
       </c>
       <c r="D1374" t="n">
-        <v>13.7403001785278</v>
+        <v>13.7399997711182</v>
       </c>
       <c r="E1374" t="n">
         <v>14.4099998474121</v>
@@ -36096,6 +36096,32 @@
         <v>14.1400003433228</v>
       </c>
       <c r="H1374" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" s="1" t="n">
+        <v>46304.5625</v>
+      </c>
+      <c r="B1375" t="n">
+        <v>10159090</v>
+      </c>
+      <c r="C1375" t="n">
+        <v>14.375</v>
+      </c>
+      <c r="D1375" t="n">
+        <v>13.7799997329712</v>
+      </c>
+      <c r="E1375" t="n">
+        <v>14.3100004196167</v>
+      </c>
+      <c r="F1375" t="n">
+        <v>14.0299997329712</v>
+      </c>
+      <c r="G1375" t="n">
+        <v>14.0299997329712</v>
+      </c>
+      <c r="H1375" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -36104,7 +36104,7 @@
         <v>46304.5625</v>
       </c>
       <c r="B1375" t="n">
-        <v>10159090</v>
+        <v>10176300</v>
       </c>
       <c r="C1375" t="n">
         <v>14.375</v>
@@ -36113,7 +36113,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="E1375" t="n">
-        <v>14.3100004196167</v>
+        <v>14.3000001907349</v>
       </c>
       <c r="F1375" t="n">
         <v>14.0299997329712</v>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -36156,7 +36156,7 @@
         <v>46308.5625</v>
       </c>
       <c r="B1377" t="n">
-        <v>14966259</v>
+        <v>15039800</v>
       </c>
       <c r="C1377" t="n">
         <v>13.0699996948242</v>
@@ -36174,6 +36174,32 @@
         <v>12.7799997329712</v>
       </c>
       <c r="H1377" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" s="1" t="n">
+        <v>46309.5625</v>
+      </c>
+      <c r="B1378" t="n">
+        <v>25154148</v>
+      </c>
+      <c r="C1378" t="n">
+        <v>12.3900003433228</v>
+      </c>
+      <c r="D1378" t="n">
+        <v>11.5500001907349</v>
+      </c>
+      <c r="E1378" t="n">
+        <v>12.3409996032715</v>
+      </c>
+      <c r="F1378" t="n">
+        <v>11.6800003051758</v>
+      </c>
+      <c r="G1378" t="n">
+        <v>11.6800003051758</v>
+      </c>
+      <c r="H1378" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -36182,7 +36182,7 @@
         <v>46309.5625</v>
       </c>
       <c r="B1378" t="n">
-        <v>25154148</v>
+        <v>25302100</v>
       </c>
       <c r="C1378" t="n">
         <v>12.3900003433228</v>
@@ -36191,7 +36191,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="E1378" t="n">
-        <v>12.3409996032715</v>
+        <v>12.3599996566772</v>
       </c>
       <c r="F1378" t="n">
         <v>11.6800003051758</v>
@@ -36200,6 +36200,32 @@
         <v>11.6800003051758</v>
       </c>
       <c r="H1378" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" s="1" t="n">
+        <v>46310.5625</v>
+      </c>
+      <c r="B1379" t="n">
+        <v>26219054</v>
+      </c>
+      <c r="C1379" t="n">
+        <v>12.6700000762939</v>
+      </c>
+      <c r="D1379" t="n">
+        <v>11.1099996566772</v>
+      </c>
+      <c r="E1379" t="n">
+        <v>11.2320003509521</v>
+      </c>
+      <c r="F1379" t="n">
+        <v>12.6300001144409</v>
+      </c>
+      <c r="G1379" t="n">
+        <v>12.6300001144409</v>
+      </c>
+      <c r="H1379" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -36208,16 +36208,16 @@
         <v>46310.5625</v>
       </c>
       <c r="B1379" t="n">
-        <v>26219054</v>
+        <v>26337300</v>
       </c>
       <c r="C1379" t="n">
-        <v>12.6700000762939</v>
+        <v>12.6899995803833</v>
       </c>
       <c r="D1379" t="n">
         <v>11.1099996566772</v>
       </c>
       <c r="E1379" t="n">
-        <v>11.2320003509521</v>
+        <v>11.2600002288818</v>
       </c>
       <c r="F1379" t="n">
         <v>12.6300001144409</v>
@@ -36226,6 +36226,32 @@
         <v>12.6300001144409</v>
       </c>
       <c r="H1379" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" s="1" t="n">
+        <v>46311.5625</v>
+      </c>
+      <c r="B1380" t="n">
+        <v>17757988</v>
+      </c>
+      <c r="C1380" t="n">
+        <v>12.6000003814697</v>
+      </c>
+      <c r="D1380" t="n">
+        <v>11.7799997329712</v>
+      </c>
+      <c r="E1380" t="n">
+        <v>12.3199996948242</v>
+      </c>
+      <c r="F1380" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="G1380" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="H1380" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -40392,7 +40392,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="H1380" t="n">
-        <v>17851500</v>
+        <v>17904700</v>
       </c>
       <c r="I1380" t="s">
         <v>9</v>
@@ -40406,10 +40406,10 @@
         <v>46314.5625</v>
       </c>
       <c r="C1381" t="n">
-        <v>12.335000038147</v>
+        <v>12.3549995422363</v>
       </c>
       <c r="D1381" t="n">
-        <v>12.3500003814697</v>
+        <v>12.3549995422363</v>
       </c>
       <c r="E1381" t="n">
         <v>11.5649995803833</v>
@@ -40421,9 +40421,38 @@
         <v>11.6700000762939</v>
       </c>
       <c r="H1381" t="n">
-        <v>10536004</v>
+        <v>10570500</v>
       </c>
       <c r="I1381" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1382" s="1" t="n">
+        <v>46315.5625</v>
+      </c>
+      <c r="C1382" t="n">
+        <v>11.3819999694824</v>
+      </c>
+      <c r="D1382" t="n">
+        <v>12.0100002288818</v>
+      </c>
+      <c r="E1382" t="n">
+        <v>11.3400001525879</v>
+      </c>
+      <c r="F1382" t="n">
+        <v>11.6599998474121</v>
+      </c>
+      <c r="G1382" t="n">
+        <v>11.6599998474121</v>
+      </c>
+      <c r="H1382" t="n">
+        <v>11087997</v>
+      </c>
+      <c r="I1382" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -40450,9 +40450,38 @@
         <v>11.6599998474121</v>
       </c>
       <c r="H1382" t="n">
-        <v>11087997</v>
+        <v>11195200</v>
       </c>
       <c r="I1382" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1383" s="1" t="n">
+        <v>46316.5625</v>
+      </c>
+      <c r="C1383" t="n">
+        <v>11.8900003433228</v>
+      </c>
+      <c r="D1383" t="n">
+        <v>12.168999671936</v>
+      </c>
+      <c r="E1383" t="n">
+        <v>11.7449998855591</v>
+      </c>
+      <c r="F1383" t="n">
+        <v>12.0500001907349</v>
+      </c>
+      <c r="G1383" t="n">
+        <v>12.0500001907349</v>
+      </c>
+      <c r="H1383" t="n">
+        <v>10136350</v>
+      </c>
+      <c r="I1383" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -40464,13 +40464,13 @@
         <v>46316.5625</v>
       </c>
       <c r="C1383" t="n">
-        <v>11.8900003433228</v>
+        <v>11.8800001144409</v>
       </c>
       <c r="D1383" t="n">
         <v>12.168999671936</v>
       </c>
       <c r="E1383" t="n">
-        <v>11.7449998855591</v>
+        <v>11.7399997711182</v>
       </c>
       <c r="F1383" t="n">
         <v>12.0500001907349</v>
@@ -40479,9 +40479,38 @@
         <v>12.0500001907349</v>
       </c>
       <c r="H1383" t="n">
-        <v>10136350</v>
+        <v>10192600</v>
       </c>
       <c r="I1383" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1384" s="1" t="n">
+        <v>46317.5625</v>
+      </c>
+      <c r="C1384" t="n">
+        <v>11.539999961853</v>
+      </c>
+      <c r="D1384" t="n">
+        <v>11.9700002670288</v>
+      </c>
+      <c r="E1384" t="n">
+        <v>11.289999961853</v>
+      </c>
+      <c r="F1384" t="n">
+        <v>11.4799995422363</v>
+      </c>
+      <c r="G1384" t="n">
+        <v>11.4799995422363</v>
+      </c>
+      <c r="H1384" t="n">
+        <v>13149698</v>
+      </c>
+      <c r="I1384" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -40508,9 +40508,38 @@
         <v>11.4799995422363</v>
       </c>
       <c r="H1384" t="n">
-        <v>13149698</v>
+        <v>13207300</v>
       </c>
       <c r="I1384" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1385" s="1" t="n">
+        <v>46318.5625</v>
+      </c>
+      <c r="C1385" t="n">
+        <v>11.3199996948242</v>
+      </c>
+      <c r="D1385" t="n">
+        <v>11.6099996566772</v>
+      </c>
+      <c r="E1385" t="n">
+        <v>11.1899995803833</v>
+      </c>
+      <c r="F1385" t="n">
+        <v>11.5200004577637</v>
+      </c>
+      <c r="G1385" t="n">
+        <v>11.5200004577637</v>
+      </c>
+      <c r="H1385" t="n">
+        <v>8563790</v>
+      </c>
+      <c r="I1385" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -40537,9 +40537,38 @@
         <v>11.5200004577637</v>
       </c>
       <c r="H1385" t="n">
-        <v>8563790</v>
+        <v>8599500</v>
       </c>
       <c r="I1385" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1386" s="1" t="n">
+        <v>46321.5625</v>
+      </c>
+      <c r="C1386" t="n">
+        <v>11.3500003814697</v>
+      </c>
+      <c r="D1386" t="n">
+        <v>11.6800003051758</v>
+      </c>
+      <c r="E1386" t="n">
+        <v>11.1213998794556</v>
+      </c>
+      <c r="F1386" t="n">
+        <v>11.4399995803833</v>
+      </c>
+      <c r="G1386" t="n">
+        <v>11.4399995803833</v>
+      </c>
+      <c r="H1386" t="n">
+        <v>11432619</v>
+      </c>
+      <c r="I1386" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -40537,7 +40537,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="H1385" t="n">
-        <v>8599500</v>
+        <v>8613100</v>
       </c>
       <c r="I1385" t="s">
         <v>9</v>
@@ -40551,13 +40551,13 @@
         <v>46321.5625</v>
       </c>
       <c r="C1386" t="n">
-        <v>11.3500003814697</v>
+        <v>11.3850002288818</v>
       </c>
       <c r="D1386" t="n">
         <v>11.6800003051758</v>
       </c>
       <c r="E1386" t="n">
-        <v>11.1213998794556</v>
+        <v>11.121000289917</v>
       </c>
       <c r="F1386" t="n">
         <v>11.4399995803833</v>
@@ -40566,9 +40566,38 @@
         <v>11.4399995803833</v>
       </c>
       <c r="H1386" t="n">
-        <v>11432619</v>
+        <v>11455100</v>
       </c>
       <c r="I1386" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1387" s="1" t="n">
+        <v>46322.5625</v>
+      </c>
+      <c r="C1387" t="n">
+        <v>11.6599998474121</v>
+      </c>
+      <c r="D1387" t="n">
+        <v>12.4694004058838</v>
+      </c>
+      <c r="E1387" t="n">
+        <v>11.6149997711182</v>
+      </c>
+      <c r="F1387" t="n">
+        <v>12.4399995803833</v>
+      </c>
+      <c r="G1387" t="n">
+        <v>12.4399995803833</v>
+      </c>
+      <c r="H1387" t="n">
+        <v>14469773</v>
+      </c>
+      <c r="I1387" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -40580,13 +40580,13 @@
         <v>46322.5625</v>
       </c>
       <c r="C1387" t="n">
-        <v>11.6599998474121</v>
+        <v>11.6499996185303</v>
       </c>
       <c r="D1387" t="n">
-        <v>12.4694004058838</v>
+        <v>12.4689998626709</v>
       </c>
       <c r="E1387" t="n">
-        <v>11.6149997711182</v>
+        <v>11.6099996566772</v>
       </c>
       <c r="F1387" t="n">
         <v>12.4399995803833</v>
@@ -40595,9 +40595,38 @@
         <v>12.4399995803833</v>
       </c>
       <c r="H1387" t="n">
-        <v>14469773</v>
+        <v>14528700</v>
       </c>
       <c r="I1387" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1388" s="1" t="n">
+        <v>46323.5625</v>
+      </c>
+      <c r="C1388" t="n">
+        <v>12.4879999160767</v>
+      </c>
+      <c r="D1388" t="n">
+        <v>12.5900001525879</v>
+      </c>
+      <c r="E1388" t="n">
+        <v>12.1010999679565</v>
+      </c>
+      <c r="F1388" t="n">
+        <v>12.3999996185303</v>
+      </c>
+      <c r="G1388" t="n">
+        <v>12.3999996185303</v>
+      </c>
+      <c r="H1388" t="n">
+        <v>10652415</v>
+      </c>
+      <c r="I1388" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -40615,7 +40615,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="E1388" t="n">
-        <v>12.1010999679565</v>
+        <v>12.1009998321533</v>
       </c>
       <c r="F1388" t="n">
         <v>12.3999996185303</v>
@@ -40624,9 +40624,38 @@
         <v>12.3999996185303</v>
       </c>
       <c r="H1388" t="n">
-        <v>10652415</v>
+        <v>10716500</v>
       </c>
       <c r="I1388" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1389" s="1" t="n">
+        <v>46324.5625</v>
+      </c>
+      <c r="C1389" t="n">
+        <v>12.2200002670288</v>
+      </c>
+      <c r="D1389" t="n">
+        <v>12.3800001144409</v>
+      </c>
+      <c r="E1389" t="n">
+        <v>11.875</v>
+      </c>
+      <c r="F1389" t="n">
+        <v>12.0600004196167</v>
+      </c>
+      <c r="G1389" t="n">
+        <v>12.0600004196167</v>
+      </c>
+      <c r="H1389" t="n">
+        <v>12428999</v>
+      </c>
+      <c r="I1389" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RGTI.xlsx
+++ b/data/RGTI.xlsx
@@ -40638,7 +40638,7 @@
         <v>46324.5625</v>
       </c>
       <c r="C1389" t="n">
-        <v>12.2200002670288</v>
+        <v>12.2399997711182</v>
       </c>
       <c r="D1389" t="n">
         <v>12.3800001144409</v>
@@ -40653,9 +40653,38 @@
         <v>12.0600004196167</v>
       </c>
       <c r="H1389" t="n">
-        <v>12428999</v>
+        <v>12511300</v>
       </c>
       <c r="I1389" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1390" s="1" t="n">
+        <v>46325.5625</v>
+      </c>
+      <c r="C1390" t="n">
+        <v>11.3500003814697</v>
+      </c>
+      <c r="D1390" t="n">
+        <v>11.5200004577637</v>
+      </c>
+      <c r="E1390" t="n">
+        <v>10.8199996948242</v>
+      </c>
+      <c r="F1390" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="G1390" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="H1390" t="n">
+        <v>14604120</v>
+      </c>
+      <c r="I1390" t="s">
         <v>9</v>
       </c>
     </row>
